--- a/results-list/g1-comerro.xlsx
+++ b/results-list/g1-comerro.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCC1614-D93F-4CA5-BE95-34B0332B83BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
-    <sheet name="Resultados-1" sheetId="1" r:id="rId1"/>
-    <sheet name="Resultados" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Resultados-1" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Resultados" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
   <si>
     <t>title</t>
   </si>
@@ -33,14 +32,14 @@
     <t>Conheça o empreendedorismo feminino no agronegócio</t>
   </si>
   <si>
-    <t>...No agronegócio, esse cenário não é diferente... — ...Transformação do agronegócio nas mãos das mulheres
+    <t xml:space="preserve">...No agronegócio, esse cenário não é diferente... — ...Transformação do agronegócio nas mãos das mulheres
 A presença feminina no agronegócio está mudando a dinâmica do setor...</t>
   </si>
   <si>
     <t>https://g1.globo.com/pr/parana/especial-publicitario/sebrae-parana/juntos-para-empreender/noticia/2024/11/09/conheca-o-empreendedorismo-feminino-no-agronegocio.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2024
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2024
  Conheça o empreendedorismo feminino no agronegócio. Subtítulo: Você sabia que a presença feminina no setor de agronegócio está crescendo? Saiba mais!
 . O setor do agronegócio no Brasil está crescendo cada dia mais, especialmente nos últimos anos. Com isso, a presença feminina também está crescendo e fortalecendo um dos principais setores em desenvolvimento no país.
 O que é o empreendedorismo feminino?
@@ -70,7 +69,7 @@
     <t>Com menos de 25 anos de emancipação, Luís Eduardo Magalhães, no oeste baiano, detém um dos maiores PIBs do estado</t>
   </si>
   <si>
-    <t>...Na Bahia, Lula participou da abertura da maior feira de agronegócios do Norte e Nordeste
+    <t xml:space="preserve">...Na Bahia, Lula participou da abertura da maior feira de agronegócios do Norte e Nordeste
 João Souza/g1
 Bahia Farm Show
 A Bahia Farm... — ...Bahia Farm Show apresenta novas tecnologias para o agronegócio
@@ -81,7 +80,7 @@
     <t>https://g1.globo.com/ba/bahia/bahia-farm-show/noticia/2023/06/08/emancipada-em-2000-conheca-luis-eduardo-magalhaes-cidade-destaque-na-producao-agricola-na-bahia.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2023
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2023
  Com menos de 25 anos de emancipação, Luís Eduardo Magalhães, no oeste baiano, detém um dos maiores PIBs do estado. Subtítulo: Antigo distrito Mimoso do Oeste, pertencente a Barreiras, município é um dos maiores produtores de soja, algodão e milho do país.
 . Luís Eduardo Magalhães, no oeste baiano, tem apenas 23 anos de emancipação política. Apesar de ser tão nova, atualmente o município detém um dos mais altos índices do Produto Interno Bruto estadual, e é um importante polo agrícola nacional.
 De acordo com o Instituto Brasileiro de Geografia e Estatística (IBGE), Luís Eduardo Magalhães ocupa a 7ª posição no ranking econômico das 417 cidades da Bahia, com um Produto Interno Bruto (PIB), de R$ 6,2 bilhões.
@@ -145,18 +144,6 @@
 Veja mais notícias do estado no g1 Bahia.</t>
   </si>
   <si>
-    <t>Caminhos sustentáveis: setores do agro apostam em práticas amigas do meio ambiente e alavancam economia</t>
-  </si>
-  <si>
-    <t>...Agronegócio pulsa em Mato Grosso do Sul; dados comprovam... — ...Antes mesmo que a sustentabilidade se transformasse em uma das premissas do agronegócio no estado e no país, já era praticada pelos...</t>
-  </si>
-  <si>
-    <t>https://g1.globo.com/ms/mato-grosso-do-sul/noticia/2022/05/23/caminhos-sustentaveis-setores-do-agro-apostam-em-praticas-amigas-do-meio-ambiente-e-alavancam-economia.ghtml</t>
-  </si>
-  <si>
-    <t>[ERRO] Navigation timeout of 30000 ms exceeded</t>
-  </si>
-  <si>
     <t>Usina Hidrelétrica de Jirau participa do Porto Velho: Oportunidades &amp; Investimentos</t>
   </si>
   <si>
@@ -166,7 +153,7 @@
     <t>https://g1.globo.com/ro/rondonia/especial-publicitario/prefeitura-de-porto-velho/porto-velho-oportunidades-e-investimentos/noticia/2024/05/21/usina-hidreletrica-de-jirau-participa-do-porto-velho-oportunidades-and-investimentos.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2024
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2024
  Usina Hidrelétrica de Jirau participa do Porto Velho: Oportunidades &amp; Investimentos. Subtítulo: A Usina de Jirau opera em Porto Velho há mais de dez anos, com 50 máquinas e 3.750 MW de capacidade instalada, cerca de 3,7% de toda a energia hidrelétrica do país
 . Mais de 40 milhões de brasileiros são abastecidos com energia renovável produzida pela Usina de Jirau. A hidrelétrica, cujo compromisso está pautado na inovação e no desenvolvimento sustentável, é a única no país que possui a certificação International Hydropower Association (IHA), selo atribuído às práticas de sustentabilidade em hidroeletricidade.
 A informação foi apresentada na última sexta-feira (17), durante a fala de Júlio Freitas, CFO da Jirau Energia, no seminário “Porto Velho: Oportunidades &amp; Investimentos”, promovido pelo jornal Valor Econômico, na sede da Federação das Indústrias de São Paulo (Fiesp). O evento reuniu resultados de empresas que operam na capital em áreas como infraestrutura, turismo, logística, agronegócio e construção civil.
@@ -186,7 +173,7 @@
     <t>https://g1.globo.com/sp/sao-carlos-regiao/especial-publicitario/banco-master/noticia/2024/02/08/master-realiza-a-compra-do-banco-voiter-antigo-indusval.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2024
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2024
  Master realiza a compra do Banco Voiter antigo Indusval. Subtítulo: Com chegada de novo banco, grupo irá dividir suas verticais de varejo e atacado
 . O Banco Master, de Daniel Vorcaro, encaminhou a compra do Banco Voiter (antigo Indusval), do empresário Roberto de Rezende Barbosa, por valores não divulgados. Com a aquisição, que ainda depende das aprovações do Banco Central e do Conselho Administrativo de Defesa Econômica (Cade), o Master passará por uma relevante reorganização societária.
 O Voiter se transformará na vertical de atacado do grupo, incorporando o banco de investimento, a corretora, as duas gestoras (MAM e MACAM) e as duas DTVMs (CM Capital e Trustee). Essa operação será comandada por Maurício Quadrado. Já o novo Banco Master, voltado ao varejo, passará a ser tocado por Augusto Lima – Vorcaro será sócio da dupla nas duas instituições.
@@ -204,7 +191,7 @@
     <t>https://g1.globo.com/sp/mogi-das-cruzes-suzano/noticia/2023/02/24/mercado-municipal-de-mogi-recebe-evento-de-promocao-da-safra-do-caqui-neste-sabado.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2023
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2023
  Mercado Municipal de Mogi recebe evento de promoção da safra do caqui neste sábado. Subtítulo: Visitantes poderão conferir e saborear as variedades, como Guiombo (popularmente conhecido como caqui chocolate), Fuyu e Rama Forte (o tipo mais plantado na cidade) Pela importância do cultivo, município é chamado de "terra do caqui".
 . Neste sábado (25), Mogi das Cruzes celebra o início da safra do caqui, fruta que garante ao município o título de “terra do caqui”, já que cerca de 50% da produção nacional é cultivada em solo mogiano. Para marcar o início da colheita, a Secretaria Municipal de Agricultura e Abastecimento da Prefeitura de Mogi realizará um evento Promoção de Safra de Caquis no Mercado Municipal, das 9h até às 15h.
 A ação especial contará com a presença de produtores, feirantes e representantes do Sindicato Rural de Mogi das Cruzes. Os frequentadores do Mercado Municipal também vão receber gratuitamente uma cartilha com informações gerais, valor nutricional, recomendações e até receitas a partir da fruta, entre elas pudim, torta, geleia e iogurte.
@@ -214,38 +201,10 @@
 O caqui é originária da Ásia: na China e no Japão, é cultivado há séculos e tão apreciado quanto a maçã. A fruta chegou a São Paulo em 1890, através dos portugueses e teve sua expansão de cultivo a partir de 1920, com os imigrantes japoneses, que trouxeram novas variedades e o domínio da produção.</t>
   </si>
   <si>
-    <t>Em entrevista ao g1, Simone Tebet fala sobre orçamento secreto, Petrobras e posicionamento no 2º turno; veja todos os trechos</t>
-  </si>
-  <si>
-    <t>...Assassinato de Bruno Pereira e Dom Phillips
-Criação de ministérios
-Alta  de combustíveis
-Desmatamento na Amazônia
-Marco temporal
-Agronegócio... — ..."Tem lugar para todos, inclusive para o agronegócio, você acaba de me permitir complementar...</t>
-  </si>
-  <si>
-    <t>https://g1.globo.com/podcast/o-assunto/noticia/2022/06/21/em-entrevista-ao-g1-simone-tebet-fala-sobre-orcamento-secreto-petrobras-e-posicionamento-no-2o-turno-veja-todos-os-trechos.ghtml</t>
-  </si>
-  <si>
-    <t>Retrospectiva 2023: confira fotos que marcaram o ano na Baixada Santista Vale do Ribeira, SP</t>
-  </si>
-  <si>
-    <t>...)
-Instituto Gremae
-Menino de 8 anos salva primo bebê de afogamento em piscina em Mongaguá (SP)
-Reprodução
-Abril
-Abril - Cargas do agronegócio...</t>
-  </si>
-  <si>
-    <t>https://g1.globo.com/sp/santos-regiao/noticia/2023/12/31/retrospectiva-2023-confira-fotos-que-marcaram-o-ano-na-baixada-santista-vale-do-ribeira-sp.ghtml</t>
-  </si>
-  <si>
     <t>Prefeitura de Cunha quer que bezerros resgatados de maus tratos sejam retirados de área cedida para hospital de campanha</t>
   </si>
   <si>
-    <t>...Reprodução
+    <t xml:space="preserve">...Reprodução
 Investigação
 A fazenda pertence a um grupo que oferecia investimento em gados para engorda, como uma oportunidade lucro no agronegócio...</t>
   </si>
@@ -253,7 +212,7 @@
     <t>https://g1.globo.com/sp/vale-do-paraiba-regiao/noticia/2022/03/03/prefeitura-de-cunha-quer-que-bezerros-resgatados-de-maus-tratos-sejam-retirados-de-area-cedida-para-hospital-de-campanha.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2022
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2022
  Prefeitura de Cunha quer que bezerros resgatados de maus tratos sejam retirados de área cedida para hospital de campanha. Subtítulo: Animais foram resgatados de fazenda onde sofriam maus tratos e levados, de forma provisória, para um hospital de campanha montado no recinto de exposições, cedido pela prefeitura. Gestão quer retirada até esta sexta-feira e veterinários alegam que animais não tem condições de transporte.
 . A prefeitura de Cunha quer que os 300 bezerros regatados de situação de maus tratos sejam retirados do terreno que ela havia cedido até esta sexta-feira (4). Após o resgate, os animais foram colocados em um hospital de campanha improvisado no espaço de eventos da cidade, cedido pela prefeitura. De acordo com os veterinários, a maioria dos animais ainda está debilitado e não tem condição de transporte.
 Os animais estão no recinto de exposições, onde aconteciam os eventos da cidade antes da pandemia, desde 7 de fevereiro, quando foram resgatados. O hospital de campanha montado no local foi feito com a autorização da prefeitura. Segundo a gestão, eles precisam ser retirados porque “o cheiro tem causado incômodo a moradores pela área estar no perímetro urbano”.
@@ -285,7 +244,7 @@
     <t>https://g1.globo.com/economia/agronegocios/noticia/2023/07/13/cogumelo-quanto-tempo-dura-pode-lavar-veja-10-dicas-para-escolher-guardar-e-preparar.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2023
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2023
  Cogumelo: quanto tempo dura? Pode lavar? Veja 10 dicas para escolher, guardar e preparar. Subtítulo: Fungo pode ser usado em pizza, quiche e até no cuscuz. No Brasil, produtores precisam simular condições climáticas da Ásia para ter shitake o ano todo.
 . Exigente, porém versátil. Nas mãos de quem adora inventar moda na cozinha, o cogumelo vira pizza, antepasto, quiche e até cuscuz.
 O g1 experimentou essas receitas com cogumelo shitake, em Piedade (SP), e aprendeu uma série de curiosidades sobre ele (veja o vídeo acima).
@@ -324,7 +283,7 @@
     <t>https://g1.globo.com/podcast/o-assunto/noticia/2022/07/12/em-entrevista-ao-g1-andre-janones-fala-sobre-educacao-basica-reforma-tributaria-religiao-e-posicionamento-no-2o-turno-veja-todos-os-trechos.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2022
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2022
  Em entrevista ao g1, André Janones fala sobre educação básica, reforma tributária, religião e posicionamento no 2º turno; veja todos os trechos. Subtítulo: Nesta segunda-feira (11), o deputado federal André Janones (Avante) foi entrevistado na série com pré-candidatos a presidente comandada por Renata Lo Prete, apresentadora do podcast 'O Assunto'. Programa foi transmitido ao vivo direto do estúdio do g1, em São Paulo, e pelo Globoplay.
 . André Janones (Avante) participou nesta segunda-feira (11) da série de entrevistas do podcast O Assunto com presidenciáveis. Ao vivo, Renata Lo Prete conversou com o pré-candidato à presidência em 2022. No vídeo acima, você confere a íntegra da entrevista, que também está disponível em áudio (abaixo).
 Veja, abaixo, todos os trechos da entrevista de André Janones ao g1:
@@ -438,7 +397,7 @@
     <t>https://g1.globo.com/ma/maranhao/noticia/2023/08/06/voce-viu-vereador-joga-dinheiro-pela-janela-da-camara-acusadas-de-matar-transexual-sao-condenadas-suspeito-de-assaltar-motorista-de-app-e-preso-e-outras-noticias-da-semana-no-g1-ma.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2023
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2023
  Você viu? Vereador joga dinheiro pela janela da Câmara, acusadas de matar transexual são condenadas, suspeito de assaltar motorista de app é preso e outras notícias da semana no g1 MA. Subtítulo: Veja quais foram as notícias em destaque ao longo da semana no portal g1 Maranhão.
 . Confira o resumo de algumas das principais reportagens e as mais acessadas pelos leitores do g1 Maranhão na semana de 30 de julho a 6 de agosto.
 • Compartilhe esta notícia no WhatsApp
@@ -493,14 +452,14 @@
     <t>MST: maior produtor de arroz orgânico do Brasil, movimento vive dificuldades para comercializar o grão</t>
   </si>
   <si>
-    <t>...O arroz orgânico do MST
+    <t xml:space="preserve">...O arroz orgânico do MST
 O discurso da agroecologia — antagônico ao agronegócio por não envolver insumos como adubo químico e agrotóxicos...</t>
   </si>
   <si>
     <t>https://g1.globo.com/economia/agronegocios/noticia/2022/09/01/mst-maior-produtor-de-arroz-organico-do-brasil-movimento-vive-dificuldades-para-comercializar-o-grao.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2022
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2022
  MST: maior produtor de arroz orgânico do Brasil, movimento vive dificuldades para comercializar o grão. Subtítulo: Movimento estima que nos últimos anos houve redução de até 40% nas compras de arroz orgânico por parte de entes públicos para alimentação escolar, área que prevê que no mínimo 30% das compras sejam feitas por meio da agricultura familiar - na qual a produção do MST se enquadra.
 . Durante sabatina no Jornal Nacional, o ex-presidente e atual candidato Luiz Inácio Lula da Silva (PT) comentou que o Movimento dos Trabalhadores Rurais Sem Terra (MST) é o maior produtor de arroz orgânico da América Latina.
 A informação foi mencionada pelo petista no telejornal para defender o movimento como um importante meio de produção rural no país.
@@ -567,7 +526,7 @@
     <t>https://g1.globo.com/go/goias/noticia/2022/12/30/retrospectiva-2022-reveja-historias-de-goias-que-viralizaram-na-web.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2022
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2022
  Retrospectiva 2022: reveja histórias de Goiás que viralizaram na web. Subtítulo: Criatividade, bom humor, perrengues e até dramas de Goiás foram destaques na internet em 2022. Milhões de visualizações, curtidas e comentários fizeram com que histórias fossem sucesso.
 . Criatividade, bom humor, perrengues e até dramas de Goiás foram destaques na internet em 2022. Milhões de visualizações, curtidas e comentários fizeram com que histórias goianas viralizassem na web e, para te relembrar das melhores, o g1 preparou uma lista.
 • Compartilhe no WhatsApp
@@ -638,7 +597,7 @@
     <t>https://g1.globo.com/saude/noticia/2022/06/04/variola-dos-macacos-hepatite-misteriosa-covid-mundo-esta-mais-propenso-a-surtos-e-epidemias.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2022
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2022
  Varíola dos macacos, hepatite misteriosa, Covid: mundo está mais propenso a surtos e epidemias?. Subtítulo: O aparecimento de novos vírus (e o ressurgimento de outros velhos conhecidos, que estavam controlados) está relacionado a sete fatores principais, que vão desde a recusa às vacinas até as mudanças climáticas.
 . As últimas semanas ficaram marcadas pelo surgimento de dois surtos que preocupam as autoridades de saúde. Primeiro, uma hepatite de origem misteriosa que acomete principalmente as crianças. Depois, o espalhamento da varíola dos macacos por vários países.
 • Compartilhe esta notícia no WhatsApp
@@ -716,14 +675,14 @@
     <t>Simone Tebet diz que tripé da campanha será economia verde, agenda social e 'governo afetivo'</t>
   </si>
   <si>
-    <t>...Simone Tebet para o Central das Eleições, na GloboNews
+    <t xml:space="preserve">...Simone Tebet para o Central das Eleições, na GloboNews
 O Assunto: Tebet defende desmatamento 'zero' e diz não ver contradição entre agronegócio...</t>
   </si>
   <si>
     <t>https://g1.globo.com/politica/eleicoes/2022/noticia/2022/07/25/simone-tebet-diz-que-tripe-da-campanha-sera-economia-verde-agenda-social-e-governo-afetivo.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2022
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2022
  Simone Tebet diz que tripé da campanha será economia verde, agenda social e 'governo afetivo'. Subtítulo: Pré-candidata do MDB participou de sabatina na 'Central das Eleições' da GloboNews. André Janones (Avante) e Ciro Gomes (PDT) serão sabatinados na terça (26) e na quarta (27).
 . A pré-candidata do MDB à Presidência da República, senadora Simone Tebet (MS), afirmou nesta segunda-feira (25) que o plano de governo de sua campanha, se homologada pelo partido, será baseada em um "tripé" composto por "economia verde", agenda social e "governo afetivo".
 "Nós temos que fazer o desenvolvimento sustentável, e economia verde é um dos tripés do nosso plano de governo. Temos um tripé muito claro, portanto, três grandes pernas a sustentar o nosso programa de governo", declarou.
@@ -790,14 +749,14 @@
     <t>'Compromisso número 1' de Lula, combate à fome terá o desafio de superar encolhimento nas ações de segurança alimentar</t>
   </si>
   <si>
-    <t>...LEIA TAMBÉM 
+    <t xml:space="preserve">...LEIA TAMBÉM 
 Recordes no agronegócio e aumento da fome no Brasil: como isso pode acontecer ao mesmo tempo?...</t>
   </si>
   <si>
     <t>https://g1.globo.com/politica/noticia/2022/11/03/compromisso-numero-1-de-lula-combate-a-fome-tera-o-desafio-de-superar-encolhimento-nas-acoes-de-seguranca-alimentar.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2022
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2022
  'Compromisso número 1' de Lula, combate à fome terá o desafio de superar encolhimento nas ações de segurança alimentar. Subtítulo: Conselho de Segurança Alimentar, Plano Nacional de Segurança Alimentar, programa Alimenta Brasil e a merenda escolar foram reduzidos nos últimos anos. Entenda como funciona cada programa.
 . O agora presidente eleito Luiz Inácio Lula da Silva (PT) afirmou no discurso de vitória neste domingo (30) que o combate à fome e à miséria é o "compromisso número 1" do governo.
 • Compartilhe no WhatsApp
@@ -886,7 +845,7 @@
     <t>https://g1.globo.com/mundo/noticia/2022/04/16/voce-viu-visitas-de-pastor-a-gabinetes-do-planalto-jornalista-esfaqueado-em-brasilia-morte-de-rincon-novidades-no-whatsapp-e-fotos-do-sol.ghtml</t>
   </si>
   <si>
-    <t>**** *pais_br *jornal_g1 *ano_2022
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2022
  Você viu? Visitas de pastor a gabinetes do Planalto, jornalista esfaqueado em Brasília, morte de Rincón, novidades no WhatsApp e fotos do Sol. Subtítulo: Uma seleção de reportagens publicadas no g1 com as notícias de 11 a 15 de abril.
 . As visitas do pastor Arilton Moura ao Planalto. O jornalista da TV Globo esfaqueado em Brasília. O julgamento do filho da deputada federal cassada Flordelis. A morte do ex-jogador Rincón. O ataque a uma estação de metrô em Nova York. A posse do novo presidente da Petrobras. Fotos do Sol com a resolução mais alta já feita até agora. A gravidez de Britney Spears.
 📩 Newsletter: receba um resumo de notícias do dia no seu e-mail
@@ -992,18 +951,374 @@
 Na verdade, a fotografia é um mosaico de 25 imagens individuais tiradas em 7 de março pelo telescópio de alta resolução Extreme Ultraviolet Imager (EUI, na sigla em inglês, ou "Imageador Ultravioleta Extremo", em tradução livre). A foto final contém mais de 83 milhões de pixels, em uma grade de 9.148 x 9.112 pixels. Segundo a própria ESA, trata-se da imagem de maior resolução do disco completo do Sol e da coroa solar já obtida.
 • Mega foto do Sol mostra forma humana? Entenda o que está por trás da imagem e o que revela a ciência</t>
   </si>
+  <si>
+    <t>Caminhos sustentáveis: setores do agro apostam em práticas amigas do meio ambiente e alavancam economia</t>
+  </si>
+  <si>
+    <t>...Agronegócio pulsa em Mato Grosso do Sul; dados comprovam... — ...Antes mesmo que a sustentabilidade se transformasse em uma das premissas do agronegócio no estado e no país, já era praticada pelos...</t>
+  </si>
+  <si>
+    <t>https://g1.globo.com/ms/mato-grosso-do-sul/noticia/2022/05/23/caminhos-sustentaveis-setores-do-agro-apostam-em-praticas-amigas-do-meio-ambiente-e-alavancam-economia.ghtml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2022
+ Caminhos sustentáveis: setores do agro apostam em práticas amigas do meio ambiente e alavancam economia. Subtítulo: Ao alinhar tecnologia com inovação, o agronegócio de Mato Grosso do Sul desponta com práticas que se preocupam socioambientalmente e garantem um futuro promissor para as novas gerações. Adotar condutas mais sustentáveis deixa de ser opção e passa a ser realidade para a conservação.
+. No estado, a expansão agropecuária ocorre em áreas já antropisadas. Essas terras, antes subutilizadas e em processo de degradação, estão sendo recuperadas, se transformando em solos férteis, que possibilitam diversos tipos de cultivos e atividades, do plantio de grãos a florestas de eucaliptos, até a pecuária de alto rendimento.
+Além da recuperação de áreas degradadas, diversas outras práticas sustentáveis foram incorporadas ao cotidiano dos produtores como: uso dos sistemas integrados, plantio direto, fixação biológica de nitrogênio e recuperação de nascentes e entre outras.
+Nesta reportagem multimídia, você vai ler os seguintes assuntos:
+• Tecnologia proporciona mais sustentabilidade no campo;
+• Entidades ajudam a disseminar conhecimento sustentável no campo;
+• Produção rural remodelada preserva mananciais;
+• Cana que produz alimento e bioenergia;
+• Modernidade nos processos rurais asseguram futuro mais sustentável;
+• Apicultura é prática secular e que tem a sustentabilidade como base;
+• Boi orgânico ajuda a preservar o Pantanal;
+• Comércio volta os olhos para consumo da proteína animal orgânica;
+• A importância da celulose para Mato Grosso do Sul;
+• Reflorestamento e Energia Verde;
+• Integração de culturas é aposta para promover a sustentabilidade no campo;
+• Da exclusividade do boi à sustentabilidade ambiental com a integração de culturas.
+Trabalho institucional
+O presidente do Sindicato Rural de Campo Grande, Alessandro Oliva Coelho, destaca o trabalho feito pelas entidades representativas do agro para levar conhecimento sobre sustentabilidade ao campo, sendo o elo entre produtores e instituições de pesquisa. Ouça acima entrevista.
+“Oferecemos palestras técnicas, capacitação de mão de obra e apoio técnico, sempre em conjunto com o Senar/MS e outras instituições. Todo o sistema sindical trabalha muito forte nessa área, para levar conhecimento ao campo. É difícil atingir a base, tendo em vista as distâncias e as dificuldades de comunicação, mas temos vários parceiros que promovem também essas iniciativas e difundem esses conhecimentos para que as informações cheguem aos mais profundos recantos do nosso estado”, explica.
+Além da parceria na propagação de informações, Alessandro explica que o Sindicato também atua em cooperação com outras entidades para atingir determinados nichos do agro. Ele cita como exemplos o trabalho com Associação Pantaneira de Pecuária Orgânica e Sustentável (ABPO) e com a Associação de Recuperação, Conservação e Preservação da Bacia do Guariroba (ARCP Guariroba).
+Outro viés de atuação, conforme Coelho, é a demanda das entidades públicas para viabilizarem pesquisas voltadas ao setor em instituições como a Embrapa, a Fundect e universidades. O presidente do Sindicato Rural lembrou, inclusive, que Mato Grosso do Sul foi um dos pioneiros no uso de sistemas integrados de produção e ainda lidera o ranking nacional, graças aos estudos desenvolvidos pela Embrapa no estado. Veja o infográfico abaixo.
+“Uma das principais demandas que temos no setor atualmente é na realização de pesquisas voltadas para o desenvolvimento de insumos biológicos, que possibilitem a redução da aplicação de agroquímicos. Isso é imprescindível, não somente para assegurar uma produção ainda mais sustentável, como para reduzir a dependência brasileira por matérias-primas para a produção desses produtos”.
+Produtores de água
+Um dos exemplos da sustentabilidade da produção do agro em Mato Grosso do Sul é o trabalho desenvolvido na Bacia do Guariroba, em Campo Grande. O principal curso de água da bacia, o córrego Guariroba é responsável por 45% do abastecimento de água potável da capital sul-mato-grossense.
+Em 1995, diante da importância do sistema para o abastecimento da cidade e para assegurar a preservação dos mananciais da bacia, foi criada a Área de Proteção Ambiental (APA) dos Mananciais do Córrego Guariroba, com uma área de 36,2 mil hectares.
+A pecuária, desde essa época, era a principal atividade econômica na APA. Entretanto, havia problemas como: acesso do gado às nascentes para a dessedentação, degradação de matas ciliares e processos erosivos.
+Em 1996 foi criada a Associação de Recuperação, Conservação e Preservação da Bacia do Guariroba (ARCP), reunindo os produtores rurais da região. Dos 67 que têm propriedades na APA, cerca de 40 participam regularmente das ações da entidade.
+Gradativamente os produtores iniciaram um trabalho de recuperação de suas áreas. Em 2009, na busca de alternativas para os problemas decorrentes de processos erosivos e diante da necessidade de recuperação e conservação da bacia foi criado o Programa Manancial Vivo (PMV).
+O programa desenvolvido pela prefeitura de Campo Grande em parceria com a Agência Nacional de Águas (ANA) e os produtores, acelerou o trabalho de restauração do potencial hídrico na bacia. Ofereceu ainda a uma parte dos produtores uma remuneração pela conservação, o Pagamento por Serviços Ambientais (PSA).
+Entre as ações implementadas estiveram:
+• Isolamento das áreas de nascentes para evitar a dessedentação do gado;
+• Recuperação de matas ciliares;
+• Instalação de curvas de nível nas áreas de pastagem para evitar o assoreamento e diminuir a velocidade da água da chuva;
+• Recuperação de pastagens degradadas.
+Quase 26 anos após a criação da ARCP, o presidente da entidade, Claudinei Menezes Pecois, aponta os resultados obtidos com o trabalho dos produtores e dos parceiros.
+Pecois explica que com a contenção e isolamento de áreas e a recuperação de 64 hectares de APPs, várias nascentes que estavam quase secas voltaram a verter água. Com isso e as outras ações desenvolvidas neste período, aumentou o volume e a qualidade da água de toda a bacia.
+“Técnicos fizeram medições em toda a bacia e apontaram que na maior parte dela a qualidade da água foi considerada boa e ótima. Além disso, houve um aumento muito grande no volume de água do córrego, mesmo no período de estiagem. Isso possibilitaria, por exemplo, até que a concessionária aumentasse, se houvesse necessidade, a capitação de água do manancial para o abastecimento de Campo Grande”.
+Apesar da importância deste trabalho, Claudinei acha que falta ainda um reconhecimento maior, pelo poder público em geral e pela população urbana que é a principal beneficiada pelo esforço e dedicação destes verdadeiros produtores de água de Campo Grande. "Poucos sabem de onde vem a água que consomem. Preservar a água sempre foi motivo de satisfação pra nós. É muito gostoso ouvir que somos 'produtores de água'. Mas falta esse reconhecimento na prática”, conclui.
+Cana: alimento e energia
+Estudos conduzidos pelos professores Maurício Roberto Cherubin, da Escola Superior de Agricultura “Luiz de Queiroz” da Universidade de São Paulo (Esalq-USP) e Glaucia Mendes Souza, do Instituto de Química da USP, apontaram que a bioenergia derivada da cana-de-açúcar é uma opção sustentável para enfrentar as mudanças climáticas e, ao mesmo tempo, fornece outros serviços ecossistêmicos essenciais e promove o desenvolvimento socioeconômico.
+Os resultados foram publicados em janeiro do ano passado pelos pesquisadores em artigo na revista científica Land, com o título “Land Use and Management Effects on Sustainable Sugarcane-Derived Bioenergy”.
+O trabalho desenvolvido pelos pesquisadores paulistas reforça uma percepção prática vivenciada pelo setor em Mato Grosso do Sul. No estado, o segmento agroindustrial é uma das principais atividades econômicas. Vivenciou uma grande expansão há pouco mais de uma década, mas cresceu alicerçado nos pilares da sustentabilidade.
+“O setor nos últimos 10 anos está vivendo uma mudança de governança muito grande. Muitas empresas eram familiares. Algumas foram incorporadas a outras. Alguns grupos cresceram e grupos internacionais entraram. Com isso, houve um reforço, uma preocupação ainda maior com aspectos, como o meio ambiente e a área social. Então a sustentabilidade se pratica há muitos anos. Não é uma coisa que veio de agora”, aponta o presidente do Conselho Deliberativo da Associação dos Produtores de Energia de Mato Grosso do Sul (Biosul MS) e diretor-presidente da União Nacional de Bioenergia, Amaury Eduardo Pekelman.
+Pekelman cita como ponto de ruptura do setor para esse novo modelo de produção a implementação da mecanização nos processos de plantio e principalmente de colheita da cana, eliminando a necessidade da queima e do corte manual feito por trabalhadores. “Foi uma ruptura muito forte no setor. Em Mato Grosso do Sul é tudo mecanizado e o estado tem a liderança nessa parte”, ressalta.
+Fábio Marquesini, gerente agrícola da usina Santa Luzia, do grupo Atvos, em Nova Alvorada do Sul, reforça a quebra de paradigma que a mecanização representou para o setor e acrescenta uma série de práticas sustentáveis adotadas na unidade e pelo setor de modo em geral.
+Uma das principais é o manejo racional da palha da cana. O volume deste subproduto varia de 10 a 15 toneladas por hectare cultivado e cerca de 80% fica no campo após a colheita mecanizada para a cobertura vegetal do solo. “Além de ajudar no controle de pragas e doenças, essa palhada me ajuda a combater a erosão, protegendo o solo dos efeitos do clima, como sol, chuva e vento; melhora os atributos do solo, retendo água e induzindo sua infiltração. Então eu só tenho benefício”, diz.
+O gerente agrícola da usina comenta que outros produtos que antes eram vistos como resíduos do setor passaram a ser encarados com alternativas economicamente viáveis e ambientalmente sustentáveis para a adubação do solo.
+A vinhaça, líquido residual do processamento do etanol, por exemplo, é rica em potássio. “Temos um plano de aplicação da vinhaça – PAV. Fazemos análise do solo em todas as áreas onde vamos aplicar e em cima desses resultados nós vemos se é compatível em receber ou não a fertirrigação com o produto”.
+Outro antigo resíduo que se transformou em adubo é a torta de filtro, que é proveniente da filtração do caldo extraído das moendas no filtro rotativo. Fábio comenta que ela tem tanto fósforo, quando potássio, mas que antes de utilizá-la, principalmente no plantio, faz uma complementação com fósforo.
+Em um contexto em que o Brasil depende da importação de fertilizantes, a utilização pelo setor sucroenergético de biofertilizantes, produzidos pelas próprias unidades usando o que antes era resíduo, se tornou uma grande vantagem econômica e ambiental.
+“Dependendo da minha análise de solo, tem algumas áreas hoje que se eu fizer somente a fertirrigação, eu não preciso fazer mais nada [ em relação a fertilizantes]. Agora tem áreas que eu preciso complementar com ureia, para fazer nitrogênio. Hoje, virou moeda de ouro, tanto a vinhaça quanto a torta aqui na Santa Luzia. Quem produz soja, quem produz milho não tem isso. Nós temos aqui, esse adubo interno”.
+Atualmente, dos 60 mil hectares agricultáveis da usina Santa Luzia, cerca de 40%, aproximadamente 22 mil recebem fertirrigação com vinhaça e metade do plantio é feita com a adubação de sua torta de filtro. Toda área de fertirrigação é monitorada constantemente para aplicação no volume adequado de acordo com a necessidade do solo.
+Para Amaury Pekelman, o grande desafio do setor é aproveitar tudo o que é gerado e, nesse sentido, avançam os estudos e pesquisas para a produção do etanol de segunda geração (2G), que utiliza como matéria-prima a palha ou bagaço da cana (que já é usado também para a produção de bioeletricidade) e do biogás e biometano, a partir da vinhaça.
+“Isso está crescendo muito. Uma montadora, por exemplo, bancou o projeto de biogás de um dos principais grupos do país, para eles contarem como redução das emissões de carbono. Então, estão surgindo negociações muito interessantes. A tendência, em um futuro próximo, é que todos os caminhões de carregamento de cana seja movidos a biogás. Ou seja, vamos produzir o nosso biogás e alimentar nossos veículos, reduzindo desse modo o consumo de combustível fóssil”.
+O presidente do Conselho da Biosul MS, entretanto, aponta que a inovação e a pesquisa tem um custo elevado e aposta no Plano Nacional de Biocombustíveis (RenovaBio), com uma ferramenta importante para que o setor e instituições parceiras tenham recursos para esses investimentos.
+O Programa prevê em sua essência que se dobre o consumo de biocombustíveis até 2030, sem para isso lançar mão de subsídio nem de imposto.
+Das 17 usinas que operam em Mato Grosso do Sul, todas já são certificadas pelo RenovaBio desde o primeiro ano de funcionamento do programa (2019/2020). Esforço que incluiu o setor entre os mais promissores na neutralização de dióxido de carbono.
+As usinas aderem voluntariamente ao RenovaBio e por um processo de auditoria monitorado pelo Governo Federal. A partir de um processo rigoroso de avaliação, recebem uma nota de eficiência energético-ambiental. Quanto mais sustentável for o processo de produção de cada unidade, maior será a nota e a conversão em Créditos de Descarbonização (CBIOs).
+Na prática, o programa reconhece o valor dos biocombustíveis como promotores de sustentabilidade ambiental, monetiza esse valor através dos CBIO, e faz com que distribuidoras de combustíveis fósseis compensem o índice de poluição dos seus produtos por meio da aquisição obrigatória desses créditos.
+Controle biológico
+Além de utilizar a tecnologia para desenvolver novos produtos, o setor sucroenergético também investe no controle biológico para enfrentar uma de suas principais pragas, a broca da cana-de-açúcar, reduzindo desse modo o uso de defensivos.
+A broca pode causar uma série de danos a cana, como: morte dos perfilho na fase inicial da cultura, reduzir a absorção e transportes de nutrientes e água, provocar enfraquecimento, brotação lateral, infecção por fungos e bactérias, redução do ATR e quebra de produtividade.
+O agente biológico usado contra a broca é a vespa Cotesia flavipes. Ela ataca a broca ainda na fase da lagarta e a enfraquece até levá-la a morte.
+“Antigamente o pessoal entrava com os copinhos para soltar as vespas no canavial. Hoje, essas vespas já vêm dentro de um copinho que é biodegradável e esse recipiente é colocado em um drone. Esse drone sai com um programa pré estabelecido, que indica o ponto exato para a soltura das vespas”, comenta o gerente agrícola da usina Santa Luzia.
+Ainda na área agrícola, o setor sucroenergético adota uma série de práticas sustentáveis como: plantio em curvas de nível, para a contenção de água, e rotação de cultura com a soja e forrageiras, como a crotalária, para fazer a conservação do solo.
+Segundo dados da Biosul MS, considerando as duas últimas safras, a produção de etanol em Mato Grosso do Sul evitou a emissão de 6,2 milhões de toneladas de dióxido de carbono – o principal gás do efeito estufa, na atmosfera.
+Apicultura como prática sustentável
+A apicultura é uma prática secular no Brasil, que a cada dia movimenta mais a economia, gerando empregos e se tornando a principal fonte de renda para muitas pessoas. Em Mato Grosso do Sul, com seus três biomas - Cerrado, Mata Atlântica e Pantanal, e com sua vocação natural para o agro, a atividade desempenha um papel fundamental, para a preservação dos ecossistemas, sendo considerada uma das práticas mais sutentáveis do segmento.
+Conforme a Organização Não Governamental (ONG) Ecologia e Ação (Ecoa), as abelhas são fundamentais na polinização de cerca de 30% de todas as plantas que são usadas na alimentação humana.
+As abelhas utilizadas na apicultura não se afastam do papel natural delas. Desta forma, a prática torna-se profundamente sustentável e altamente rentável.
+“A apicultura preenche todos os três requisitos do tripé da sustentabilidade. É uma atividade economicamente viável, é socialmente justa e ambientalmente correta. É uma atividade que não precisa desmatar para produzir. O apicultor depende da natureza em harmonia para ele produzir, então é a atividade que menos impacta”, detalha o biólogo especialista em abelhas, Marcos Wolf.
+Adriano Adames de Souza, 53 anos, é um conceituado apicultor de Mato Grosso do Sul. Há 30 anos trabalha com abelhas e atualmente vê nelas a única fonte de renda da família.
+“Eu sou pioneiro, na minha família não tem ninguém que é apicultor, mas eu me apaixonei pela apicultura há muito tempo. Eu era pecuarista pequeno e todos os anos eu tinha que vender um pouco. Todo ano eu vendia os bezerros e ainda assim, se eu não me apertasse muito, eu tinha que vender uma ou duas vacas para cobrir as coisas”, lembra Adriano.
+Foi então que ele conheceu a apicultura e fez uma escolha que mudaria a vida dele para sempre. “Eu me dediquei à apicultura, estudei bastante e tomei a decisão de vender tudo o que eu tinha, o meu gado, vendi tudo e investi na apicultura. Hoje eu sou um produtor de mel conceituado, estou no mercado há muitos anos, não tenho mais gado. Não me arrependo nenhum minuto disso”, afirma.
+Desde a década de 1990, Adriano acompanha as mudanças e evoluções da apicultura no estado. “O apelo pela alimentação saudável tem aumentado muito o consumo per capita de mel. Isso na economia repercute como o dinheiro para o apicultor em si, saúde para quem consome e para os pequenos produtores, que produzem pouco mel, também passa a ser a segunda fonte de renda ou muitas vezes a ser a principal”, comenta.
+Ele é um dos apicultores assistidos pelo Serviço Nacional de Aprendizagem Rural (Senar) de Mato Grosso do Sul. De acordo com o coordenador técnico do Sistema Famasul, André Nunes, aproximadamente 300 apicultores recebem assistência técnica do Senar/MS em todo o estado. O número de colmeias registradas no estado junto à Agência Estadual de Defesa Sanitária Animal Vegetal (Iagro) ultrapassa 28 mil.
+Da parceria com as abelhas não é utilizado somente o mel, mas também a cera e outros produtos. “No estado há entre 10 e 12 indústrias que fazem o envase e compra de todo esse mel. Possuímos indústrias que fazem o processamento de cera, isso gera mão de obra também, é comercializado na indústria cosmética”, cita André.
+Criação
+Para o cultivo de abelhas, vários fatores devem ser levados em consideração, como a localização e organização das colmeias, o manejo e a oferta de alimentos às abelhas. Com relação a este último, é imprescindível analisar a florada local, conforme orienta o biólogo especialista em abelhas, Marcos Wolf.
+“A florada é quando tem um conjunto de plantas florindo ou uma única espécie. Então tem épocas, que seria a nossa primavera, que vai ter uma abundância de flores e a abelha vai guardar o excesso de néctar e transformar em mel e ter um estoque ali, é o momento que a gente colhe”, explica.
+Em períodos de baixa florada, as abelhas ficam sem muitas opções de plantas para colherem o néctar e transformá-lo em mel para se alimentar. Desta forma, outras formas de alimentação podem ser utilizadas.
+“Geralmente se utiliza o xarope de açúcar e algum complemento para suprir a parte proteica”, cita o biólogo. Ou então, é fornecido outro tipo de florada às abelhas, como detalha o apicultor Adriano.
+“Nós temos aqui na apicultura um ciclo de floração, que é na primavera, que é a floração do Cerrado. Quando termina a floração do Cerrado, eu tenho uma propriedade parceira onde a gente tem abelha, que tem o Cerrado e do lado tem uma plantação de eucalipto. Quando termina a primavera, entra a floração do eucalipto, então eu continuo produzindo mel, só que de uma floração diferente”, relata.
+O biólogo Marcos completa que a florada interfere diretamente no mel produzido. “Se a florada muda, a cor, o gosto do mel muda também. Dessa forma, há uma infinidade de combinações que podem ser exploradas de abelhas e floradas na produção do mel”, destaca.
+Além dos cuidados com a localização e alimentação das abelhas, a forma em que elas são manejadas requer atenção do apicultor e funcionários.
+“Primeiramente ele deve ter os equipamentos de proteção individuais, o fumegador, o macacão, botas, luvas, tem que estar bem protegido. Tem que tomar cuidado também com o local que ele vai criar as abelhas, se não é perto de casas, próximo à criação de animais, para não oferecer risco. Tem que ser um local seguro e o manejo sempre usando o fumegador para as abelhas não ficarem irritadas. Fazendo o manejo correto ele mantém a segurança tanto da colônia, quanto dele e de quem tiver em torno também”, explica Marcos.
+Retorno gratificante
+O apicultor sul-mato-grossense, Adriano Adumes de Souza, ressalta que ao longo dos 30 anos em que atua com abelhas o que prevalece é a gratidão. Atualmente, possui entre 300 e 350 colmeias distribuídas na propriedade que tem e em outras de parceiros. Ele ressalta que a parceria com outros setores é fundamental.
+“O pecuarista tem a área legal, a área que ele não pode ocupar, e a gente pode colocar abelhas lá e fazer uma parte da ecologia, contribuindo com a natureza. Hoje é uma cadeia que depende do outro”, opina.
+Após três décadas, o pequeno pecuarista tornou-se um grande apicultor, gerando renda, trabalho e consciência ambiental.
+“Eu lembro como se fosse hoje do primeiro balde de 20kg que eu tirei e depois eu lembro do meu primeiro tambor de 200 litros. De lá para cá eu só sei que a coisa vem aumentando a cada ano”, conta com orgulho.
+Boi orgânico
+A história da pecuária no Pantanal sul-mato-grossense já tem mais de 200 anos. Antes mesmo que a sustentabilidade se transformasse em uma das premissas do agronegócio no estado e no país, já era praticada pelos criadores da região, que adotaram as práticas de manejo do gado às peculiaridades do bioma, conciliando a produção com a preservação ambiental.
+Dados de várias instituições apontam o Pantanal como o bioma brasileiro com a maior cobertura natural preservada, 87,5% do território - segundo o Instituto Brasileiro de Geografia e Estatística (IBGE) -que inclui vegetal florestal, campestre e áreas úmidas, sendo que cerca de 90% dessas áreas são privadas, ou seja, são mantidas pelos produtores.
+Para atender as oportunidades de um mercado cada vez mais exigente e a própria evolução da atividade, a produção de gado que em algumas propriedades já sustentável no Pantanal, foi aprimorada para a criação do chamado boi orgânico.
+A carne orgânica, produzida a partir destes animais, além de ser um produto que engloba muita tecnologia, é um dos tipos de proteína animal mais sustentável. O protocolo de manejo assegura aos criadores uma produção mais consciente com o animal, meio ambiente e consumidores. Além de ser um conceito que ganha cada vez mais adesão.
+Em 2021 foram quase 40 mil cabeças de gado abatidas dentro do sistema orgânica no Brasil, o triplo do registrado em 2020, conforme a Associação Brasileira de Proteína Orgânica (ABPO). Em crescente, a Carne Orgânica pantaneira, além de conservar a biodiversidade do bioma, vem ganhando novos mercados, como pesquisadores comentam.
+LEIA TAMBÉM
+• Criadores de gado em MS usam novas estratégias para proteger o meio ambiente
+• Valor da produção agropecuária de MS deve chegar a R$ 82,5 bilhões em 2022, diz ministério
+• Faturamento com produção agropecuária em MS em 2021 pode ter sido 16% maior que o de 2020
+Várias regras devem ser seguidas para que o gado seja considerado orgânico. Para que a proteína seja atestada, o produtor rural deve fazer com que a produção siga o sistema “orgânico” e submeter o processo a uma certificadora, que gerará um selo assegurando a produção orgânica ao consumidor.
+Para que o produtor rural “ganhe” o selo, a certificadora inspeciona a propriedade e elenca cerca de 50 tópicos em que a produção deve seguir, desde a forma de manejo do gado às leis trabalhistas entre os funcionários. Os itens foram elencados pelo Ministério da Agricultura e Pecuária (Mapa) e a Empresa Brasileira de Pesquisa Agropecuária (Embrapa).
+Para que o boi seja considerado orgânico, o animal deve ser criado livre, solto em pasto sem nenhum tipo de adubação química, já que as gramíneas servem de alimento e, se tiverem algum tipo de agrotóxico, o gado deixa de ser orgânico. Além da pastagem, os animais podem se alimentar com rações, desde que sejam orgânicas e o sal mineral introduzido na dieta não contenha ureia.
+Os tratamentos de qualquer doença ou feridas nos animais não podem ser feitos com antibióticos, apenas com homeopatia ou fitoterapia. Se o produtor recorrer a qualquer tipo de medicamento convencional, o animal também deixa de ser considerado orgânico. As vacinas obrigatórias são aceitas no processo. Veja o infográfico abaixo.
+Carne orgânica é prática pesquisada no Pantanal
+O conceito "carne orgânica" nasceu na virada deste século, no início dos anos 2000. O professor e pesquisador da Embrapa Pantanal, Urbano Abreu, foi um dos pioneiros no processo no Brasil. Em 2004, ainda pensando apenas em uma pecuária “sustentável” no Pantanal, os cientistas caminharam os estudos para o que é o boi orgânico hoje.
+Além da ajuda da Embrapa Pantanal, o projeto teve amparo e auxílio da WWF-Brasil e da ABPO, com o objetivo de estabelecer a pecuária orgânica de forma certificada para os produtores do bioma. Atualmente, Urbano explica que existem seis propriedades rurais na região pantaneira que adotam, exclusivamente, este tipo de sistema em Mato Grosso do Sul.
+Urbano comenta que a carne orgânica é um produto saudável, certificado e produzido com o máximo de responsabilidade social, levando em consideração a saúde e bem estar dos animais e o meio ambiente. “O processo de produção - desde o nascimento, criação, engorda, abate e destino final - é rastreado e auditado. Isso garante uma confiabilidade enorme aos consumidores, além da transparência no processo. A pessoa sabe que animal é aquele que está no prato dela, é confiança”.
+Não é apenas o consumidor que possuí vantagens ao comer um produto mais sustentável e responsável com o meio ambiente. O pecuarista da região do Pantanal que se dedica à produção de uma proteína sustentável pode ter isenção de até 50% do Imposto sobre Circulação de Mercadorias e Prestação de Serviços (ICMS), e aqueles que produzem carne orgânica, a isenção pode chegar a 67%.
+A pecuária é a principal atividade econômica da região pantaneira e vem sendo desenvolvida de maneira extensiva há mais de 200 anos. "A crescente produção de carne orgânica e sustentável pode ser uma opção capaz de contribuir para que se mantenham as boas condições de conservação ambiental do bioma”, afirma o pesquisador.
+A carne orgânica ainda é destinada a um público específico, como Urbano destrincha. Este nicho de público busca por práticas socialmente e ambientalmente corretas e que possuem preocupações com a utilização de aditivos químicos nos produtos.
+“Os processos de pecuária orgânica seguem critérios de qualidade que incentivam a conservação ambiental, a saúde humana, os direitos dos trabalhadores e o bem-estar animal. Em especial, para os certificados premium e gourmet e de vínculo com a origem”, finaliza o pesquisador.
+Paixão pelo Pantanal atrelada ao empreendedorismo e sustentabilidade
+Foi lá no início dos anos 2000 que o produtor rural Leonardo Barros procurou o irmão, Luciano Barros, com a proposta de mudar alguns rumos das fazendas que a família tem no Pantanal. Juntos, separaram uma das propriedades para “testar realmente se o negócio do boi orgânico ia dar certo. Deu!”. Atualmente, a empresa de Leonardo faz todo o processo para comercialização da proteína animal, entenda um pouco mais no vídeo acima.
+“A gente estava olhando o mercado e as pessoas estavam procurando um produto sustentável, que tivesse rastreabilidade e fosse amigo do meio ambiente. Nós estamos no Pantanal há 200 anos. Fomo em busca da certificação. Meu irmão era zootecnista, acostumado no remédio [aditivos químicos], achou que não ia dar certo. Partimos para um teste. Início dos anos 2000, pegamos uma pequena fazenda, certificamos e começamos a levar a sério”, explicou Leonardo sobre o início da lida com os bois orgânicos.
+Atualmente são três propriedades rurais da família dedicas exclusivamente à produção de animais orgânicos. Além das propriedades rurais, o empresário e proprietário rural possui um complexo que gere todo o processo da proteína animal: desde a criação à venda em gôndolas.
+A partir de 2019, Leonardo, junto da sobrinha Mariana Barros, ampliaram o ramo e começaram a industrializar o produto. Antes, alugando o espaço para o processamento do alimento, hoje, são proprietários de um pequeno frigorífico em Campo Grande que processa cerca de 30 toneladas de carne orgânica, da desossa à embalagem dos produtos que vão para vários locais do Brasil.
+“A gente compra animais de outros associados. 80% é de gado próprio. Nós vendemos carne orgânica do Pantanal. Os grandes centros, como São Paulo, Rio de Janeiro e Brasília já existem um grande público que consome este produto. A grande maioria do nosso produto vai para fora, 90%”, comenta Mariana.
+A empresa familiar mescla o empreendedorismo com a paixão pelo Pantanal e pelo boi pantaneiro. Em contato direto com o bioma, Leonardo explica que os produtos vendidos levam uma mensagem de consumo consciente e de que o bioma oferece importantes contribuições.
+“O Pantanal é nossa vida. A Mariana foi para o Pantanal mamando e morou lá três anos”, disse Leonardo, e Mariana complementou a fala do tio: “Pantanal é sinônimo de amor, eu lembro do meu pai falando do Pantanal e por isso me emociono. É um amor muito grande que temos por este lugar”. Assista ao vídeo acima.
+Entre as missões da empresa está: “levar um pedaço do Pantanal para casa das pessoas através da carne orgânica pantaneira”. Leonardo explica que as alterações na produção da proteína animal fazem com que o produto possua diferenças daqueles convencionais já ofertados no mercado. A empresa possuí os seguintes princípios:
+• Garantia de um manejo natural e imbuindo a tradição pantaneira;
+• Bem-estar animal;
+• Preservação ambiental;
+• Ganho social;
+• Manutenção da cultura do homem pantaneiro;
+• Aplicação de novas tecnologias adaptadas.
+“Nós falamos de um ambiente em que a Embrapa já catalogou mais de 30 tipos de gramínea. Nossos animais vivem e comem as mesmas gramíneas dos herbívoros que vivem no Pantanal, é um produto especial. A gente trabalha com o que acredita, vendemos aquilo que vivemos”, comenta Leonardo.
+Mariana afirma que o tratamento dos animais nas propriedades destinadas ao sistema orgânico é feito da forma correta em relação às exigências. “Processo empático com animal. Os animais são criados livres, com outros bichos no Pantanal, comendo a vegetação nativa. Eles são criados da forma mais natural possível, no seu habitat possível”.
+Para que esse tratamento fosse possível, lá no começo, Leonardo teve que retirar todos os indícios de agrotóxicos das propriedades, já que os animais não podem comer pastagem com aditivo químico. O pecuarista comenta que além do ponto dos aditivos, a busca por tratamentos fitoterápicos e homeopáticos foram cruciais para que as fazendas fossem categorizadas como orgânicas.
+Em Campo Grande, além da indústria, a Bio Carnes conta com uma boutique que oferece atendimento aos consumidores de maneira individualizada. Além dos cortes embalados para consumo imediato, as carnes são vendias em peças para churrasco e kits de consumo semanal. No açougue são comercializados carnes do tipo sustentável, que abrange outras regras menos rígidas em comparação às do processo orgânico.
+“As pessoas acham que a carne orgânica é cara, mas a nossa não. A nossa carne está no patamar das outras casas de carnes ‘premium’. Como fazemos todo o processo da proteína, nós conseguimos comercializá-la com o preço mais em conta. Queremos que o nosso público aumente em Campo Grande e que as pessoas da nossa terra, o Pantanal, passe a consumir mais o produto que é daqui”, finalizou Mariana.
+Florestas plantadas: tudo é reaproveitado
+A cadeia de produção da celulose é umas das principais da economia sul-mato-grossense. O estado, inclusive, é o maior exportador brasileiro de celulose de fibra curta. Somente nos quatro primeiros meses do ano embarcou 1,3 milhão de toneladas para outros países, movimentando US$ 443,9 milhões, o equivalente a R$ 2,1 bilhões. Os dados são apresentados pelo Ministério da Economia.
+Entretanto, a cadeia depende da matéria-prima produzida no campo: as florestas cultivadas (silvicultura). O estado tem mais de 1 milhão de hectares cultivados, principalmente com eucalipto.
+A produção florestal é uma atividade focada na sustentabilidade e contribui com inúmeros benefícios para o agronegócio, como: a absorção de carbono na atmosfera, melhora da qualidade do solo e da água, redução da pressão do desmatamento e degradação de florestas naturais, e outros proveitos para o meio ambiente.
+De acordo com o Indústria Brasileira de Árvores (Ibá), o Brasil é o segundo país com a maior área de florestas do mundo, possuindo cerca de 7,84 milhões de hectares de florestas cultivadas (1 hectare equivale a 1 campo de futebol oficial). Desse total, 5,6 milhões de hectares são florestas plantadas sustentáveis de espécies de eucalipto ou pinus.
+O engenheiro florestal Marcelo Morais de Freitas, explica que as árvores se desenvolvem aliando produtividade, equilíbrio do ecossistema e a melhoria ambiental das comunidades ao seu entorno.
+“A silvicultura tem a característica de ser um posto de trabalho permanente, uma floresta tem atividades em todos os ciclos. Na área florestal tudo é reaproveitado, todos os processos podem ser otimizados e bem pensado, visando a produção sustentável”, disse.
+Segundo dados do Ministério da Agricultura, Pecuária e Abastecimento (MAPA), divulgados no último Boletim Casa Rural da Federação de Agricultura e Pecuária (Famasul), a celulose exportada no primeiro trimestre de 2022, corresponde a 99,13%, sendo o principal produto florestal exportado em Mato Grosso do Sul.
+• Investimento bilionário em fábrica de celulose deve fazer cidade de MS 'nascer de novo'
+Sem risco de sofrer com a escassez de madeira, o estado conta com uma grande reserva da matéria prima para abastecer fábricas de celulose que se instalam em Mato Grosso do Sul. Além de gerar desenvolvimento, a atividade produtiva pode e deve ser aliada à preservação do meio ambiente.
+A Eldorado Brasil é uma empresa de base florestal, com 250 mil hectares de florestas plantadas no Mato Grosso do Sul e outros 115 mil hectares de conservação. Em Três Lagoas (MS) - a 325 quilômetros de Campo Grande - a companhia opera uma fábrica com capacidade para produzir em ritmo de 1,8 milhão de toneladas de celulose branqueada por ano e a usina termelétrica Onça Pintada.
+Além das áreas destinadas as florestas plantadas, a Eldorado possui aproximadamente 30% do total das áreas destinadas a conservação ambiental contemplando Áreas de Preservação Permanente (APP), Áreas de Reserva Legal (ARL) e outras Áreas de Interesse Ecológico. A empresa conquistou as principais certificações nacionais e internacionais, atestando a adoção de práticas socioambientais responsáveis em toda cadeia produtiva.
+O gerente de sustentabilidade da empresa de celulose, Fábio de Paula, esclarece que produtos de origem florestal estão presentes no nosso dia a dia e vão desde os mais evidentes, como papel e móveis, até produtos de beleza, medicamentos, acessórios, pneus, alimentos e roupas.
+“A madeira produz a celulose e a fábrica extrai o produto final, que é a celulose branqueada de eucalipto. Através dela é possível produzir o papel, alimentos, curativos, máscaras, papel moeda, é uma infinidade de produtos”, disse.
+Energia verde
+O processo de extração da celulose gera toneladas de resíduos passíveis de serem reaproveitados, o que contribui para agregar valor às cadeias produtivas e diminuir os impactos ambientais. A Eldorado Brasil, por meio de um projeto pioneiro no país, gera energia verde tendo como matéria-prima a biomassa produzida a partir de tocos e raízes de eucaliptos que antes ficavam no solo e eram descartados. Veja vídeo abaixo.
+Com isso, as partes de madeira das árvores que não são empregadas na fabricação de celulose, geram energia limpa e renovável. Para a geração de energia é previsto o uso de mil toneladas de biomassa por dia.
+O gerente de sustentabilidade reitera que através do reaproveitamento de resíduos do eucalipto que seriam descartados, é possível produzir energia 100% limpa e renovável, suficiente para abastecer uma cidade de 700 mil habitantes, o que equivale a seis vezes a população de Três Lagoas. Segundo ele, uma árvore é auto suficiente para produzir energia renovável, tornando a produção ainda mais eficiente e sustentável, dentro do conceito da economia circular.
+“A energia verde vem proveniente do eucalipto, ou seja, é uma energia renovável. Temos a possibilidade de fazer o maior aproveitamento da floresta”, destaca.
+Fábio reitera que são utilizadas máquinas para realizar a pré-trituração de tocos de eucalipto, o peneiramento para remoção das impurezas e a trituração final, visando o maior aproveitamento da produção florestal. Segundo ele, novas tecnologias têm aumentado a eficiência da produção florestal e diminuído ainda mais seu impacto ambiental. Veja o infográfico abaixo.
+“Além da celulose, é possível gerar energia limpa atrás das árvores, contribuindo para a matriz elétrica do Brasil e a redução das mudanças climáticas. Através do arranquio de tocos e raízes de eucalipto não utilizados é produzida uma biomassa que também é encaminhada para as usinas termelétricas para a produção energia verde. Com isso, temos uma matriz energética muito sustentável, otimizando as etapas da produção florestal e a redução das mudanças climáticas”.
+Além da biomassa de tocos, através das árvores é possível produzir a biomassa de madeira inservível, que consiste no reaproveitamento de madeira que sofreu alguma avaria, como pragas, doenças, incêndios e mortes naturais, e que não serve para o processo produtivo de celulose.
+Reflorestamento
+Essenciais no ecossistema para frear os efeitos das mudanças climáticas e desastres naturais, as árvores realizam a fotossíntese resultando na produção de oxigênio para a vida na terra. Durante anos a prática de desmatamento sem grandes preocupações devastou a produção florestal, em razão disso, ações para equilibrar o ritmo da extração de madeiras têm sido cada vez mais necessárias.
+O engenheiro florestal Marcelo Morais de Freitas avalia que o reflorestamento é sinônimo de preservação ambiental e também de bem-estar da população. Ele reitera que além de abastecer fábricas na produção da celulose e energia verde, as árvores em constante crescimento, sequestram carbono da atmosfera através do processo de fotossíntese.
+Entre os impactos positivos da sustentabilidade florestal, o especialista destaca a manutenção da cobertura vegetal, a conservação de habitats animais e o equilíbrio do regime hídrico, além da manutenção de nutrientes e permeabilidade do solo.
+Segundo ele, a utilização de florestas plantadas pela própria indústria garante que florestas nativas sejam preservadas. Além disso, a preservação da biodiversidade é assegurada pelo uso de técnicas específicas de plantio e corredores de vegetação nativa.
+“O processo de crescimento do eucalipto leva em torno de seis a sete anos, durante esse período a árvore tem o poder de capturar o carbono da atmosfera e liberar o oxigênio, o que é extremamente sustentável. Além disso, com o aumento da floresta e conservação de áreas naturais, podemos contribuir com a flora e também com o avistamento de animais”, destaca.
+Com isso, é fato que o consumo inteligente de recursos florestais e a produção de energia verde geram benefícios para toda sociedade.
+Agricultura visa boas práticas
+A demanda por alimentos cresce a cada dia em todo mundo. Por isso, a agricultura precisa cada vez mais de técnicas de produção sustentáveis que asseguram rentabilidade aos produtores, alimentos de qualidade para os consumidores e respeito a natureza, de modo a assegurar a curto e longo prazo a continuidade da produção sem a degradação do solo, do ar ou dos recursos hídricos.
+Em Mato Grosso do Sul, um dos grandes produtores brasileiros de grãos (quinto de soja e quarto de milho), a agricultura deu um salto na última década, graças a inovação, tecnologia e investimento dos agricultores, mas sempre com a preocupação de fazer o manejo adequado dos recursos naturais, evitando a degradação ambiental.
+A área cultivada com grãos, por exemplo, cresceu, em uma década (da safra 2011/2012 a 2021/2022) 80,1%, de acordo com o Companhia Nacional de Abastecimento (Conab), passando de 3,256 milhões de hectares para 5,891 milhões de hectares, enquanto que a produção aumentou 77,8%, de 11,610 milhões de toneladas para 20,650 milhões de toneladas.
+Uma das grandes ferramentas utilizadas pelos produtores são as técnicas de manejo sustentável do solo, o que inclui plantio direto, plantio em curvas de nível, rotação de cultura, uso de sistemas integrados, preservação de áreas de proteção permanentes (APPs), recuperação de áreas degradadas e de nascentes e ainda reposição de matéria orgânica, entre outras.
+Ao comentar sobre as técnicas de manejo, o agrônomo e especialista em ciência de solos da Embrapa Gado de Corte, Manuel Macedo, destacou a importância do plantio direto e depois da rotação de culturas para a recuperação de áreas degradas.
+“O plantio direto é uma das técnicas que se tem utilizado para se ter uma agricultura mais sustentável porque a lavoura de grãos, por exemplo, ela melhora a fertilidade do solo. A maioria dos solos do Brasil Central e da região do Cerrado são bastante fracos, pois são solos ácidos e com baixa fertilidade. Então a agricultura recupera a fertilidade do solo e pela venda dos grãos o custo é reduzido, já que a utilização de insumos na pastagem pode ser muito caro para o pecuarista", afirmou o especialista.
+A rotação com pastagem tem também um papel importante de proteger o solo da erosão. Além de melhorar as propriedades físicas do solo, permite um melhor escoamento de água, uma infiltração mais eficiente e possibilita que as plantas desenvolvam um sistema radicular mais profuso e profundo.
+Herança de boas práticas
+Já na quinta geração de produtores rurais, o agrônomo Mateus Arantes, de 49 anos, explica que manter a sustentabilidade na agricultura, com o tripé econômico, social e ambiental, sempre fez parte da tradição de sua família.
+“O meu pai já tinha essa visão sustentável de manejo de pasto, além de manter sempre as nascentes cercadas e protegidas e de proporcionar o melhor para o funcionário. Na minha família, acreditamos que são as pessoas que fazem a sustentabilidade, então essa preocupação vem desde o meu avô”, explicou.
+Para a família Arantes, o sucesso vem de um trabalho coletivo, em que os colaboradores são bem assistidos, para que a produção gere renda e esse lucro possa ser revertido na melhoria da produção, aumento da produtividade e preservação ambiental.
+“Entre as práticas sustentáveis que adotamos na fazenda, em primeiro lugar temos a reserva ambienta. Não abrimos mão de ter essas áreas de preservação permanente, rios, nascentes e a própria reserva legal. Pensamos sempre duas vezes antes de arrancar uma árvore na área de produção. E em segundo lugar, como principal técnica na agricultura, usamos o plantio direto”.
+Para o agrônomo, a grande diferença dos solos antigos para os atuais, é o conhecimento. ”Na época do meu vô ele não sabia, não tinha uma técnica, era tudo feito na base da grade, do arado, não havia um manejo correto com o gado, não tinha um manejo correto com a agricultura. Então os bois degradavam muito rápido as pastagens por falta de conhecimento de como manejar”.
+Recursos sustentáveis
+Do ponto de vista ambiental, com a agricultura sustentável se protege mais o solo e os recursos hidrícos, melhorando assim a biodiversidade.
+“Como se altera o ciclo das culturas a fauna e a flora do solo se diversificam de modo que a produção fica numa posição meio intermediária entre a pastagem permanente e a vegetação natural. De alguma maneira nós já tiramos a vegetação natural para produzir alimentos, agora o que temos que fazer é melhorar a situação dos solos onde o homem já abriu, para que a gente produza grãos, fibras, energia de forma eficiente e sustentável”, explica Manuel Macedo.
+O especialista em solos aponta que é visual a mudança nas lavouras do estado com a melhoria da qualidade dos solos.
+“Se viajarmos para o sul do estado, é surpreendente ver como o solo está coberto. Foi plantado soja, agora plantaram milho com a braquiária, então daqui a pouco o milho vai ficar maduro, vai ser colhido e vai ficar a braquiária. O terreno vai continuar coberto e verde nas áreas de integração até meados de agosto, quando começa o período de seca mais intensa, quando o déficit hídrico é mais elevado. Antes, nessa mesma época, o terreno ficava descoberto, as áreas todas revolvidas, gradeadas, hoje já não é mais assim. Então o impacto em toda essa região foi muito grande. Nesse quesito MS melhorou drasticamente”, apresenta Manuel.
+Integrar para avançar
+A integração é um dos principais instrumentos da produção sustentável no agronegócio sul-mato-grossense. O sistema oferece uma série de vantagens aos produtores, como: otimização do uso da terra, aproveitamento de todo o potencial do solo e combinação de vários modelos e culturas, em um mesmo espaço.
+A intensificação, dependendo da modalidade adotada, possibilita a produção em uma mesma área de: grãos, fibras, madeira, energia, leite ou carne, e que a associação pode ser feita de forma consorciada, em sucessão ou em rotação.
+Mato Grosso do Sul, que expandiu sua produção baseada na conversão de áreas, principalmente em espaços que eram ocupados anteriormente somente por pastagens, lidera o ranking nacional de uso da integração.
+O estado tem 3,169 milhões de hectares ocupados com esse modelo de produção, segundo a Rede ILPF – associação formada por empresas e pela Embrapa para difundir esses sistemas. A área representa 18,1% do total do pais, que chega a 17,431 milhões de hectares.
+Agregar diferentes culturas em áreas comum tem sido a estratégia para se obter mais lucros, melhor aproveitamento ambiental e ainda reduzir perdas. Esse equilíbrio do que é produzido em uma mesma propriedade rural tem feito a diferença em prol da sustentabilidade ambiental. É o caso do produtor rural Gabriel Garcia Nascimento.
+Na Fazenda Cerejo, em Angélica, os 7 mil hectares tradicionalmente voltados para a pecuária foram dando espaço para a soja, e com o tempo, também para a cana-de-açúcar.
+“No início da década de 90 a gente começou a introduzir novas tecnologias. Nas áreas de pecuária a gente entrava com soja. E fomos reformando pasto, aumentando a quantidade de bebedouros. Em 2007 foi construída a usina e a gente começou a plantar cana”, resume o produtor rural.
+A experiência inicial deu certo e hoje, a fazenda trabalha com a integração entre as três culturas. Uma vai ajudando a outra. Do pasto ao bolso dos trabalhadores, passando pela sustentabilidade ambiental.
+“Acaba tendo renda do boi, da cana, da soja. Agora, com as áreas de irrigação, a gente tem o milho também. Então, dificilmente você tem todas as culturas com preço baixo. Todas elas acabam se complementando, e, no fim do ano, o faturamento acaba aumentando”, fala Gabriel.
+A preocupação com a proteção ambiental também é outra razão para a o trabalho de integração entre as culturas. O produtor define: “Da forma que a gente vem trabalhando, os dejetos acabam se transformando em adubo. Então, você não usa o químico”.
+“Por exemplo: a gente planta soja de novembro a março. Na mesma área, a gente coloca a pecuária de março até novembro. Nas áreas de cana, eu faço um ciclo de cinco anos. Depois, um ciclo de soja. A soja fixa nitrogênio no solo, que também serve depois como adubo para a cana, coloca pasto ali. Então você acaba aumentando sua renda e o pasto de inverno gera um pouco de potássio, que é uma necessidade depois da soja. Depois, volta para a cana outra vez”.
+Todo esse ciclo de integração entre as culturas na fazenda resulta, em média, em 200 toneladas anualmente de cana. Produto que é vendido para a economia local.
+Na pecuária, a produção é de 15 arrobas por hectare/ano, que vão para exportação. Quantidade bem superior a média nacional, que é de duas a três arrobas. As 60 sacas por hectare/ano, de soja, também são vendidas para o mercado internacional. Em relação ao milho, o que é produzido é comercializado com cooperativas da região.
+“Com a pandemia, o agro demonstrou ser o motor do país. Eu acho que ainda mais com 
+[...TRUNCADO]</t>
+  </si>
+  <si>
+    <t>Em entrevista ao g1, Simone Tebet fala sobre orçamento secreto, Petrobras e posicionamento no 2º turno; veja todos os trechos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...Assassinato de Bruno Pereira e Dom Phillips
+Criação de ministérios
+Alta  de combustíveis
+Desmatamento na Amazônia
+Marco temporal
+Agronegócio... — ..."Tem lugar para todos, inclusive para o agronegócio, você acaba de me permitir complementar...</t>
+  </si>
+  <si>
+    <t>https://g1.globo.com/podcast/o-assunto/noticia/2022/06/21/em-entrevista-ao-g1-simone-tebet-fala-sobre-orcamento-secreto-petrobras-e-posicionamento-no-2o-turno-veja-todos-os-trechos.ghtml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**** *pais_br *jornal_g1 *ano_2022
+ Em entrevista ao g1, Simone Tebet fala sobre orçamento secreto, Petrobras e posicionamento no 2º turno; veja todos os trechos. Subtítulo: Candidata do MDB participou nesta segunda-feira (20) da série de entrevistas comandadas por Renata Lo Prete, apresentadora do podcast ‘O Assunto’, com pré-candidatos à Presidência da República. Entrevista foi transmitida ao vivo direto do estúdio do g1, em São Paulo.
+. Simone Tebet (MDB) participou nesta segunda-feira (23) da série de entrevistas do podcast O Assunto com presidenciáveis. Ao vivo, Renata Lo Prete conversou com a pré-candidata à presidência em 2022. No vídeo acima, você confere a íntegra da entrevista, que também está disponível em áudio (abaixo).
+Veja, abaixo, todos os trechos da entrevista de Simone Tebet ao g1:
+• 3ª via
+• Polarização política
+• Fome
+• Trabalho e informalidade
+• Assassinato de Bruno Pereira e Dom Phillips
+• Criação de ministérios
+• Alta de combustíveis
+• Desmatamento na Amazônia
+• Marco temporal
+• Agronegócio
+• Crise climática
+• Caso Genivaldo
+• Armas
+• Militares e política
+• Posturas autoritárias no governo Bolsonaro
+• Saúde pública
+• Teto de gastos
+• Aborto
+• CPI da Pandemia
+• Orçamento Secreto
+• Formalização da candidatura
+• Papel das mulheres na candidatura
+• Machismo na política
+• Apoio do marido
+• Eleições e as urnas eletrônicas
+• Reeleição
+• Cadeia produtiva da cultura
+• Segundo turno
+3ª via
+Se colocando como uma pré-candidata do "centro democrático do Brasil", Simone Tebet criticou a briga política entre esquerda e direita no país. Para ela, a polarização "está levando o Brasil para o abismo". E ainda defendeu: "Nós temos condições de nos apresentar como a única alternativa capaz de pacificar o Brasil".
+Veja a declaração no trecho abaixo.
+Polarização política
+Durante a sua entrevista a Renata Lo Prete, Tebet citou mais de uma vez a polarização política no Brasil. "Não podemos esquecer que o atual presidente é fruto de um desgoverno do passado. Não vamos esquecer que essa polarização, esse discurso de ódio – de nós contra eles – não vem de agora", disse.
+"Para mim, está muito claro isto: Bolsonaro é fruto dos excessos, dos equívocos e dos erros do Partido dos Trabalhadores."
+Fome
+Atualmente, 33,1 milhões de pessoas não têm o que comer. O número é quase o dobro do contingente estimado em 2020. Quando foi questionada sobre o que faria para lidar com a situação, a pré-candidata à presidência afirmou:
+"O objetivo principal da minha candidatura é erradicar a miséria. Erradicar mesmo. Diminuir a pobreza é outra coisa. Mas não é possível se admitir, num país da grandeza como o nosso, ter uma única criança dormindo com fome todos os dias".
+Trabalho e informalidade
+Atualmente, cerca de 40% da população ocupada está em postos informais no país, segundo o Instituto Brasileiro de Geografia e Estatística (IBGE). Para a pré-candidata, a educação de jovens é o primeiro passo para combater a informalidade no mercado de trabalho. Junto a isso, a senadora avalia que o crescimento econômico do país também faz parte da solução. "O Brasil voltando a crescer, automaticamente você abre novas portas de emprego", disse.
+Tebet também defendeu o projeto no Senado do novo ensino médio, que teve seu voto, e começou a ser implementado neste ano.
+Assassinato de Bruno Pereira e Dom Phillips
+O assassinato de Bruno Pereira e Dom Phillips foi um dos temas abordados durante a entrevista com Simone Tebet. Sobre o caso, a candidata lamentou que Jair Bolsonaro (PL) tenha se omitido diante das investigações e criticou a postura do presidente:
+“Um presidente da República, num caso desse, não pode estar numa motociata no estado do Amazonas, enquanto você está num processo de investigação num caso gravíssimo como esse”, afirmou, em referência ao ato do presidente realizado no sábado (18) em Manaus.
+Criação de ministérios
+Uma das propostas de Tebet é recriar o ministério do Planejamento e Orçamento. A pré-candidata citou a importância da pasta para a economia do país e criticou o desempenho do PIB durante o governo Bolsonaro.
+"Por que o Orçamento está engessado e sequestrado pelo Centrão? Porque o presidente da República, o governo federal, não tem projeto de país. Não tinha projeto nem antes da pandemia. Não adianta culpar a pandemia pelos problemas, basta olhar os indicativos econômicos, o PIB brasileiro não cresceu 2% no primeiro ano do presidente."
+Alta dos combustíveis
+Simone Tebet se posicionou contra a privatização da Petrobras e responsabilizou a gestão do presidente Jair Bolsonaro pela crise dos combustíveis. Para a senadora, a medida resultaria na perda do "mínimo de controle" do governo sobre a estatal.
+"O problema da Petrobras é outro. É que nós temos um presidente da República que não sabe o que fazer com ela porque é incompetente e terceiriza os problemas que não sabe resolver", disse.
+Tebet afirmou ainda que o ex-presidente Lula fez da pauta da estatal "uma política ideológica para se manter no poder".
+Desmatamento na Amazônia
+Simone Tebet defendeu que os militares brasileiros sigam atuando na Amazônia em conjunto com as polícias e os órgãos de controle. Para ela "as Forças Armadas são extremamente importantes para defender a fronteira e a soberania nacional".
+Ela disse também que é preciso "fortalecer os órgãos de fiscalização e controle para evitar e impedir o desmatamento ilegal".
+Marco temporal
+Simone Tebet afirmou que é seu dever aceitar e seguir qualquer decisão tomada pelo Supremo Tribunal Federal (STF) a respeito do marco temporal na demarcação de terras indígenas.
+"Eu, como operadora do direito, tenho que me curvar ao posicionamento e decisão do Supremo Tribunal Federal".
+Agronegócio
+A candidata defendeu o estímulo do governo federal à energia limpa, à emissão de créditos de carbono e reforçou a necessidade da preservação da Floresta Amazônica.
+Segundo ela, para que o Brasil readquira importância na diplomacia ambiental, são necessários reforços em órgãos de fiscalização e controle na Amazônia para zerar o desmatamento ilegal na região.
+Crise climática
+Sobre o espaço da crise climática dentro do seu governo, a pré-candidata à Presidência da República pelo MDB afirmou que há lugar para todos, "inclusive para o agronegócio".
+"Tem lugar para todos, inclusive para o agronegócio, você acaba de me permitir complementar. Os rios voadores da Amazônia estão comprovados. Pelo menos um terço das chuvas que chegam no meu estado, no sul do meu estado [MS], no PR, em SC e no RS, que é quem hoje está sofrendo mais com a seca por conta do desmatamento da Amazônia... Esses rio voadores dependem da floresta, da umidade, porque, se não ele para antes da hora, ele não vem tão carregado de chuva, ele não cai no meu estado, ele não cai no Sul", afirmou ela.
+Caso Genivaldo
+A entrevistada condenou as ações tomadas pela Polícia Rodoviária Federal (PRF) no caso Genivaldo, homem negro que foi morto no fim do mês passado em Sergipe por asfixia dentro do porta-malas de uma viatura após policiais jogarem gás de pimenta . A senadora diz ainda que, fosse presidente, teria colocado a direção da PRF "na rua".
+"Entendo que lugar de bandido é na cadeia, mas quem julga é a Justiça. O policial não tem direito nem de exterminar nem de fazer pré-julgamentos. Ele tem que cumprir rigorosamente a Constituição".
+Armas
+A pré-candidata disse ser a favor do armamento das mulheres no campo, mas se mostrou contrária ao avanço das armas para a população em geral.
+"A pauta do Brasil não é essa, o Brasil precisa de paz. Pergunta para as mulheres, que são a maioria da população brasileira, se ela quer uma arma na mão dos seus companheiros, uma arma na mão até dos seus filhos. A pauta do Brasil é outra", afirmou a senadora.
+Militares e política
+Simone Tebet afirmou que o governo do presidente Jair Bolsonaro (PL) "flerta com o autoritarismo" e "tenta politizar as Forças Armadas".
+"Nós temos um governo que, sim, flerta com o autoritarismo. Sim, flerta. Porque, no meu ver, não representa a direita, mas a extrema-direita no Brasil. E que tenta, que tenta politizar as Forças Armadas brasileiras. Mas eu confio muito nas Forças Armadas brasileiras, acho que está muito amadurecida, ela é muito responsável e está pronta para defender a democracia", disse ela.
+Posturas autoritárias no governo Bolsonaro
+Simone Tebet disse não acreditar que as pessoas que elegeram o presidente Jair Bolsonaro em 2018 imaginavam que ele fosse ter atitudes tão autoritárias durante seu mandato. Como exemplo, ela falou da “briga acirrada” entre o presidente e outras instituições como a imprensa e o Supremo Tribunal Federal (STF). “Ninguém imaginava chegar a essa proporção”, disse.
+Saúde pública
+A pré-candidata do MDB foi perguntada sobre como aumentar o orçamento da saúde pública do país, que em 2022 teve queda em relação ao ano anterior.
+Ela afirmou que precisa “remodelar” o orçamento e colocar a pessoa pobre como prioridade.
+“Colocando o pobre como prioridade absoluta [no orçamento]. Hoje no Brasil, não é isso que acontece”.
+Teto de gastos
+Simone Tebet afirmou que defende o “teto de gastos”, mas com uma “nova roupagem”. Segundo ela, o “teto de gastos” é demonizado porque o dever de casa “não foi feito”.
+Tebet ainda fez uma relação entre o teto de gastos de o orçamento secreto. "Se não fosse o teto de gastos no Brasil, quanto seria o orçamento secreto?”, questionou.
+Aborto
+Simone Tebet, que já demonstrou ser contra revisitar as possibilidades de legalização do aborto no país além do que já é permitido por lei, classificou como inconstitucional uma cartilha sobre o assunto divulgada pelo Ministério da Saúde. “É inconstitucional, não vale de nada”, afirmou Tebet.
+CPI da Pandemia
+A pré-candidata à Presidência da República Simone Tebet reprovou a postura do Procurador da República, Augusto Aras, após o encerramento da Comissão Parlamentar de Inquérito (CPI) da Covid. Ela deu nota zero, numa escala de zero a dez. “Do procurador? Zero”.
+Orçamento Secreto
+Simone Tebet afirmou na entrevista que o “orçamento secreto" é a nova forma de comprar consciência de parlamentares” e sem transparência nenhuma.
+Segundo a pré-candidata, esses recursos criam uma concorrência desleal com pessoas que querem entrar na vida política e não podem competir com os parlamentares. Para Tebet, o orçamento é uma “forma de ferir a democracia”.
+Formalização da candidatura
+Ao comentar sobre a formalização da sua candidatura, Simone Tebet afirmou que tem “absoluta certeza” de que o MDB irá até o fim do processo eleitoral ao seu dela. Segundo ela, o nome dela foi se consolidando a partir de três reuniões da executiva do MDB e de outros partidos que declararam apoio.
+"Eu não sou candidata pelo MDB, eu me apresento como pré-candidata de três partidos. O MDB tem história, o MDB tem responsabilidade, ele não vai tirar uma candidatura depois de já ter feito exatamente esse compromisso."
+Papel das mulheres na candidatura
+Simone Tebet também abordou na entrevista a presença de mulheres na política. “Nós precisamos de mais mulheres na política”, disse.
+A pré-candidata foi questionada sobre uma foto na qual aparece acompanhada de diversos políticos homens e de cor branca. A foto mostra ainda que ela, por sua vez, participa de forma remota da reunião sendo a única mulher. A pré-candidata afirmou que a foto representa a “cara da política brasileira”.
+"Temos apenas 15% de mulheres na política, e não é porque mulher não se interessa em política ou porque não vota em mulher", disse.
+Machismo na política
+A pré-candidata do MDB à Presidência da República em 2022 afirmou que é preciso reconhecer que o Brasil é um país violento com as mulheres. “É lamentável dizer que o Brasil é muito violento com suas mulheres”.
+Ao comentar episódios de agressões políticas, Simone Tebet disse que é uma tentativa de afastar a participação feminina da política e contou que já chorou ao sofrer esse tipo de violência. “A primeira vez que cometeram essa violência contra mim, eu fui no banheiro chorar”.
+Apoio do marido
+Simone Tebet falou sobre o apoio que recebe de seu marido, Eduardo Rocha, para a disputa eleitoral em 2022. Ela comemorou o fato do marido, que também é político, ter uma “alma feminina” e ser um “ser político por natureza”.
+Segundo Tebet, Rocha afirmou que ela tem uma “missão pelo país”. “Ele, simplesmente, parou na vida pública”, disse Simone.
+Eleições e as urnas eletrônicas
+“Se, porventura, chegar no segundo e eu perder as eleições, serei a primeira a declarar. Isso é democracia”. Essa foi a declaração de Simone Tebet sobre uma possível derrota nas eleições.
+Ela afirmou se contentar com o resultado das urnas, diferentemente das declarações controversas do presidente Jair Bolsonaro sobre a credibilidade do processo eleitoral. Além disso, Simone disse estar convicta de que estará no segundo turno.
+Reeleição
+Ao responder a uma pergunta de um ouvinte do podcast O Assunto, Simone Tebet defendeu o fim da reeleição e mandato de cinco anos para presidente da República. Para a pré-candidata do MDB, a possibilidade de reeleição faz com que os presidentes topem "qualquer coisa" para se reeleger, ainda que isso "quebre" o Brasil.
+"A reeleição foi um erro no Brasil. [...] E ela só serve para que, no final dos seus governos, no último ano, e foram todos, todos que passaram fizeram isso, que sejam capazes de fazer qualquer coisa, ainda que quebrar o Brasil ou quebrar estatais."
+Cadeia produtiva da cultura
+Simone Tebet afirmou que pretende recriar o Ministério da Cultura em um possível governo. Ela defendeu ainda que algumas pastas tenham orçamento que não possam receber cortes, entre elas Cultura e Educação. Tebet afirmou: “Cultura é vida é arte, é história. Nós não podemos viver sem cultura”.
+Segundo turno
+A pré-candidata do MDB na eleição presidencial de outubro, Simone Tebet afirmou que tem confiança de que avançará ao segundo turno. E, caso não avance para a segunda etapa do pleito, ela afirmou que estará "em um palanque eleitoral defendendo a democracia".</t>
+  </si>
+  <si>
+    <t>Retrospectiva 2023: confira fotos que marcaram o ano na Baixada Santista Vale do Ribeira, SP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...)
+Instituto Gremae
+Menino de 8 anos salva primo bebê de afogamento em piscina em Mongaguá (SP)
+Reprodução
+Abril
+Abril - Cargas do agronegócio...</t>
+  </si>
+  <si>
+    <t>https://g1.globo.com/sp/santos-regiao/noticia/2023/12/31/retrospectiva-2023-confira-fotos-que-marcaram-o-ano-na-baixada-santista-vale-do-ribeira-sp.ghtml</t>
+  </si>
+  <si>
+    <t>[ERRO] Navigation timeout of 50000 ms exceeded</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1341,16 +1656,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="55" customWidth="1"/>
     <col min="3" max="3" width="83.109375" customWidth="1"/>
     <col min="4" max="4" width="73.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1364,7 +1679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1381,7 +1696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1398,236 +1713,236 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D15" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86266708-F626-4D1C-A02B-1D4771CD88AD}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1643,49 +1958,55 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>67</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="14.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>71</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="14.4" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
 </worksheet>
 </file>